--- a/parts.xlsx
+++ b/parts.xlsx
@@ -85,445 +85,416 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="36" customWidth="1"/>
-    <col min="3" max="3" width="44" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="60" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="7" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="40" customWidth="1"/>
+    <col min="7" max="7" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Item</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Section</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Item</t>
-        </is>
-      </c>
       <c r="C1" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Price (₹)</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Qty</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Price (₹)</t>
-        </is>
-      </c>
       <c r="E1" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Note</t>
+          <t xml:space="preserve">Per</t>
         </is>
       </c>
       <c r="F1" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Only if</t>
+          <t xml:space="preserve">Vendor</t>
         </is>
       </c>
       <c r="G1" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Key</t>
+          <t xml:space="preserve">Description</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LED channels (2 m)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t xml:space="preserve">LED channels</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{LED_channels} channels · {Channel_cm} cm each</t>
+      <c r="C2" s="3">
+        <v>50</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7 LED channels</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aluminium channel, cut to 27 cm and painted black</t>
         </is>
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LED strip WS2812B (5 m roll)</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">LED channels ({Length_cm/100} m)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ROUNDUP(LED_channels/Channels_per_length,0)</t>
-        </is>
-      </c>
-      <c r="D3" s="3">
-        <v>50</v>
+          <t xml:space="preserve">LED channels</t>
+        </is>
+      </c>
+      <c r="C3" s="3">
+        <v>1365</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">{Channels_per_length} channels cut from each</t>
+          <t xml:space="preserve">20 LED channels</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">channel</t>
+          <t xml:space="preserve">60 LEDs/m, 15 LEDs in each channel</t>
         </is>
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2510 4-pin connectors</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">LED strip WS2812B ({Roll_m} m roll)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ROUNDUP(LED_channels*LEDs_per_channel/LEDs_per_m/Roll_m,0)</t>
-        </is>
-      </c>
-      <c r="D4" s="3">
-        <v>1365</v>
+          <t xml:space="preserve">LED channels</t>
+        </is>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4">
+        <v>2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">{LED_channels*LEDs_per_channel/LEDs_per_m} m · {LEDs_per_channel} LEDs per channel at {LEDs_per_m}/m</t>
+          <t xml:space="preserve">LED channel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">strip</t>
+          <t xml:space="preserve">One at each end of a channel</t>
         </is>
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filament (1 kg)</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2510 4-pin connectors</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LED_channels*2</t>
-        </is>
-      </c>
-      <c r="D5" s="3"/>
+          <t xml:space="preserve">Nodes</t>
+        </is>
+      </c>
+      <c r="C5" s="3">
+        <v>1349</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 per LED channel</t>
+          <t xml:space="preserve">37 nodes</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">conn2510</t>
+          <t xml:space="preserve">About 27 g per node</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Node PCBs</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t xml:space="preserve">Nodes</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{Nodes} nodes</t>
+      <c r="C6" s="3"/>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">other node</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">General Node board</t>
         </is>
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Central nodes</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Filament (1 kg)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ROUNDUP(Nodes*Node_grams/1000,0)</t>
-        </is>
-      </c>
-      <c r="D7" s="3">
-        <v>1349</v>
+          <t xml:space="preserve">Nodes</t>
+        </is>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7">
+        <v>1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">{Nodes*Node_grams/1000} kg · {Node_grams} g per node</t>
+          <t xml:space="preserve">central node</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">filament</t>
+          <t xml:space="preserve">Central Node board</t>
         </is>
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Touch sensors</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Node PCBs</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nodes-Central_nodes</t>
-        </is>
-      </c>
-      <c r="D8" s="3"/>
+          <t xml:space="preserve">Nodes</t>
+        </is>
+      </c>
+      <c r="C8" s="3">
+        <v>9.5</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 per node, central nodes apart</t>
+          <t xml:space="preserve">touch sensor</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcb</t>
+          <t xml:space="preserve">₹19 a pair</t>
         </is>
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESP32-ETH01</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Central nodes</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Central_nodes</t>
-        </is>
-      </c>
-      <c r="D9" s="3"/>
+          <t xml:space="preserve">Network and control</t>
+        </is>
+      </c>
+      <c r="C9" s="3">
+        <v>792</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 per hexagon</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">central</t>
+          <t xml:space="preserve">hexagon</t>
         </is>
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ethernet cables</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Touch sensors</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nodes-Sensors_left_out</t>
-        </is>
-      </c>
-      <c r="D10" s="3">
-        <v>9.5</v>
-      </c>
+          <t xml:space="preserve">Network and control</t>
+        </is>
+      </c>
+      <c r="C10" s="3"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 per node · {Sensors_left_out} left out · ₹19 a pair</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">touch</t>
+          <t xml:space="preserve">hexagon</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 V 10 A power supply</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t xml:space="preserve">Network and control</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 per hexagon</t>
+      <c r="C11" s="3">
+        <v>1115</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hexagon</t>
         </is>
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Drywall screws</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESP32-ETH01</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hexagons</t>
-        </is>
-      </c>
-      <c r="D12" s="3">
-        <v>792</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">esp</t>
+          <t xml:space="preserve">Miscellaneous</t>
+        </is>
+      </c>
+      <c r="C12" s="3">
+        <v>1.4</v>
+      </c>
+      <c r="D12">
+        <v>2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">node</t>
         </is>
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M3 screws</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ethernet cables</t>
-        </is>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ethernet</t>
+          <t xml:space="preserve">Miscellaneous</t>
+        </is>
+      </c>
+      <c r="C13" s="3">
+        <v>3.5</v>
+      </c>
+      <c r="D13">
+        <v>3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">node</t>
         </is>
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M3 nuts</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 V 10 A power supply</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hexagons</t>
-        </is>
-      </c>
-      <c r="D14" s="3">
-        <v>1115</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">psu</t>
+          <t xml:space="preserve">Miscellaneous</t>
+        </is>
+      </c>
+      <c r="C14" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="D14">
+        <v>3</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">node</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M3 × 6 mm standoffs</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t xml:space="preserve">Miscellaneous</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">per node</t>
+      <c r="C15" s="3">
+        <v>4.4</v>
+      </c>
+      <c r="D15">
+        <v>3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">node</t>
         </is>
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Backboard</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drywall screws</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nodes*2</t>
-        </is>
-      </c>
-      <c r="D16" s="3">
-        <v>1.4</v>
+          <t xml:space="preserve">Miscellaneous</t>
+        </is>
+      </c>
+      <c r="C16" s="3"/>
+      <c r="D16">
+        <v>1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 per node</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">drywall</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M3 screws</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nodes*3</t>
-        </is>
-      </c>
-      <c r="D17" s="3">
-        <v>3.5</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3 per node</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">m3</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M3 nuts</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nodes*3</t>
-        </is>
-      </c>
-      <c r="D18" s="3">
-        <v>0.95</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3 per node</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nut</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M3 × 6 mm standoffs</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nodes*3</t>
-        </is>
-      </c>
-      <c r="D19" s="3">
-        <v>4.4</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3 per node</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">standoff</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Backboard</t>
-        </is>
-      </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20" s="3"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{Backboard_size}</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Backboard</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">board</t>
+          <t xml:space="preserve">backboard</t>
         </is>
       </c>
     </row>
@@ -636,28 +607,13 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roll_m</t>
+          <t xml:space="preserve">Node_grams</t>
         </is>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">strip comes in rolls of this many metres</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Node_grams</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>27</v>
-      </c>
-      <c r="C8" t="inlineStr">
         <is>
           <t xml:space="preserve">grams of filament per printed node</t>
         </is>
@@ -670,7 +626,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="1" width="120" customWidth="1"/>
+    <col min="1" max="1" width="140" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -690,98 +646,84 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">If something in it is wrong, the app shows which cell, and the server log lists it too.</t>
+          <t xml:space="preserve">If something is wrong, the app shows which cell, and the server log lists it too.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parts sheet</t>
+          <t xml:space="preserve">Parts sheet: one row per item</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A row with a Section starts a new section; the Note on that row is the section's note. Rows under it with an Item are its items.</t>
+          <t xml:space="preserve">Item: its name. Section: the heading it goes under; sections appear in the order they first come up.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Qty: a number, a formula, or blank for not known yet. Formulas are typed as plain text, e.g. Nodes*3 or ROUNDUP(LED_channels/7,0).</t>
+          <t xml:space="preserve">Price (₹): price for one, in rupees. Blank shows -- and leaves it out of the totals.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Price (₹): price for one, in rupees; blank shows -- and leaves it out of the totals.</t>
+          <t xml:space="preserve">Qty and Per: how many, counted per something on the wall. The total is rounded up.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Item and Note may hold {formula} placeholders, filled in with the number, e.g. "{Nodes} nodes".</t>
+          <t xml:space="preserve">     3 per node · 1 per hexagon · 2 per LED channel · 1 per 7 LED channels (one 2 m length gives 7 channels)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Only if: an optional formula; the row is listed only when it is not 0. Backboard is 1 when the backboard is on.</t>
+          <t xml:space="preserve">     Per can be: wall, hexagon, node, central node, other node (every node but the central ones), touch sensor, LED channel, backboard.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Key: a short id the build guide uses to remember edits to a row. Keep it when renaming an item; new rows can leave it blank.</t>
+          <t xml:space="preserve">     Leave Per blank for a fixed number for the whole wall. Leave Qty blank if not known yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     backboard is 1 when the backboard is on and 0 when off; an item that comes to 0 is left off the list.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Names formulas can use</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">From the wall: Hexagons, Nodes, Central_nodes, LED_channels, Sensors_left_out, Backboard, Backboard_size (text, for notes).</t>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vendor: shop link, phone or name. Description: anything else. Both show on the build guide (page 4), where they can be changed for one guide.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">From the Settings sheet: every Name there. A setting may use the settings above it.</t>
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Settings sheet</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Functions: ROUNDUP, ROUNDDOWN, ROUND, MIN, MAX, with + - * / and brackets.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Settings sheet</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The build guide also uses Channel_cm, Length_cm, Channels_per_length, LEDs_per_channel, LEDs_per_m and Node_grams, so keep those rows.</t>
+          <t xml:space="preserve">Numbers the build guide uses in its steps and channel drawing. Keep every row; a value may be a formula on the rows above, e.g. ROUNDDOWN(Length_cm/Channel_cm,0).</t>
         </is>
       </c>
     </row>
